--- a/backend/app/modules/safety_ledgers/templates/company-vehicle-template.xlsx
+++ b/backend/app/modules/safety_ledgers/templates/company-vehicle-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JSI\besma-safety-ledgers-deploy\backend\app\modules\safety_ledgers\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0DC2C8C7-5D2C-431E-8811-CC4417D1EB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B212FA91-A469-4BE4-8039-88CE9E8DE87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{C9DCD448-5B91-451B-BD9E-6C6FDA5165E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F993CB72-CFA0-4A47-8A7B-02FB9C885679}"/>
   </bookViews>
   <sheets>
     <sheet name="7월" sheetId="16" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{993C2AFE-4172-4C7A-9D73-F819F4180767}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{95D1EC60-224D-42FB-806A-65986BD0E903}">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{D905250B-044C-418C-9510-43448239C304}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{C5D700CD-C427-4D4C-BCCF-168B6A1AD4ED}">
       <text>
         <r>
           <rPr>
@@ -229,7 +229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{14E41025-AF0A-4CE6-8828-ADC67B9414F6}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{16839870-D1DB-4A6E-BA2C-55AFC3E94AD9}">
       <text>
         <r>
           <rPr>
@@ -329,7 +329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{1A4773B6-7B35-4BE7-8393-72043495441C}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{486797B6-12D1-49A7-B527-7EBB7EF7AA5A}">
       <text>
         <r>
           <rPr>
@@ -427,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{E0C128C3-4668-4BA7-A33A-257B3BE3CFD8}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{0B9A84C6-738B-4EF3-9979-E5D5B66C7407}">
       <text>
         <r>
           <rPr>
@@ -517,7 +517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B8EACC74-385A-4902-8993-F9524C8988A8}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{DB778A24-0D49-4815-B82C-321D36FA156D}">
       <text>
         <r>
           <rPr>
@@ -665,7 +665,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{24536426-DCF7-456C-95FA-02C3EFE681F1}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{85CFC2CF-C126-4AE9-A6BB-302CFE77F695}">
       <text>
         <r>
           <rPr>
@@ -826,7 +826,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{ABFE7B2E-BF15-4CC9-B18A-060F6E2E543E}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{A6FD7804-2673-4FF8-8FBD-0EDFBE876C32}">
       <text>
         <r>
           <rPr>
@@ -925,7 +925,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{49FB1EA9-AA1F-4B38-ACA4-26F63287F33F}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{F437A754-4A36-4634-900F-0295F0E00657}">
       <text>
         <r>
           <rPr>
@@ -951,7 +951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{312A546E-70D8-4D65-89D3-B8D4D424382A}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{8B8AF1FA-578E-4F5C-A13B-2DD7E7C64726}">
       <text>
         <r>
           <rPr>
@@ -1124,7 +1124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{AEAD6B54-BE67-4287-86D9-7E0B16D5F761}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{24ED9133-E675-4BBE-B8CD-60CDB818B4A6}">
       <text>
         <r>
           <rPr>
@@ -1224,7 +1224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{7EA00330-183F-4439-A8D0-1CDBA6C94BB8}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{F50FB37D-9D6F-4FBE-BD55-418D2080FE29}">
       <text>
         <r>
           <rPr>
@@ -1322,7 +1322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{27AD76B3-92C8-48F6-8975-B003F5AAFF29}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{D466BD6F-E46C-4FA0-8E4E-F59FE19E11F4}">
       <text>
         <r>
           <rPr>
@@ -1412,7 +1412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{CC5D5CE5-888F-421A-8BE4-323E1A73339F}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{9BE6C63C-9B69-40C2-B038-F1587CF6E633}">
       <text>
         <r>
           <rPr>
@@ -1560,7 +1560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{55BA629E-6A71-455C-8D94-23F7FDD0A7D4}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{A845B4D4-C2EC-49BA-871B-86B931FFA9C4}">
       <text>
         <r>
           <rPr>
@@ -1721,7 +1721,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{BC430026-6B8D-4C7B-97AC-1720289BFA29}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{C6BFE0B2-313B-46C8-8AEB-B23D4DFF8997}">
       <text>
         <r>
           <rPr>
@@ -2489,7 +2489,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC59AAB9-B692-B05C-DF06-9A226A8BCB0A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F2019F9-C08F-AC2C-87F1-89D98612EB8C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2954,7 +2954,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A37E83A-76A5-5314-BB4C-86904DC2CB67}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D48073E6-E26F-88CE-37BB-179A4039A156}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3234,7 +3234,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35D0AF45-CEDC-405D-BC56-E0F17199E67A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EFF0427-BDFD-42DA-AC19-7E42647C195B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3699,7 +3699,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E795DDD-8A19-4463-8467-EC116EA498B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FFC9221-51EF-4824-B921-9E4CD0795E92}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4216,7 +4216,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52227EDF-D32F-4639-942D-57F82224615F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF01455-E267-43CE-9B09-79A2EC381E9E}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4748,10 +4748,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{DD5962D8-FFDB-4F15-9D8F-AB2FF66B6188}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{C6A085E8-371D-4B7E-8D00-B1EA21CB0E44}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{9B05D902-EB9D-487E-8087-87B962B7FD7B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{AD021761-02CD-4068-BDCC-99CB438F1249}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4765,7 +4765,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E03AB2-B82B-4F45-A9FF-4E4A81E1ED05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECC3E6B-479A-468D-8AB6-BE36FAAC032D}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5297,10 +5297,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{5EBCB5F8-FDD6-4748-B9A6-4E41EB8E35F0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{633F6023-D18D-4196-A452-84EAC496AF62}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{FF1AE2EE-E71C-40D9-B909-ED3D39F11CB5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{0635E5A5-16FA-4F1C-8197-E92AC2ACB734}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/app/modules/safety_ledgers/templates/company-vehicle-template.xlsx
+++ b/backend/app/modules/safety_ledgers/templates/company-vehicle-template.xlsx
@@ -8,17 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JSI\besma-safety-ledgers-deploy\backend\app\modules\safety_ledgers\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B212FA91-A469-4BE4-8039-88CE9E8DE87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{88B07AF5-0C9F-4C4C-9793-9509B9B9D903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F993CB72-CFA0-4A47-8A7B-02FB9C885679}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{CB2AFB4F-771C-472A-8EBD-756E310E9CF4}"/>
   </bookViews>
   <sheets>
     <sheet name="7월" sheetId="16" r:id="rId1"/>
     <sheet name="8월" sheetId="17" r:id="rId2"/>
+    <sheet name="9월" sheetId="18" r:id="rId3"/>
+    <sheet name="10월" sheetId="19" r:id="rId4"/>
+    <sheet name="11월" sheetId="20" r:id="rId5"/>
+    <sheet name="12월" sheetId="21" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'10월'!$A$1:$H$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'11월'!$A$1:$H$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'12월'!$A$1:$H$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'7월'!$A$1:$H$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'8월'!$A$1:$H$41</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'9월'!$A$1:$H$41</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -30,7 +38,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{95D1EC60-224D-42FB-806A-65986BD0E903}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{E2C23149-5D37-4375-85CB-6F3C70B004DE}">
       <text>
         <r>
           <rPr>
@@ -56,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{C5D700CD-C427-4D4C-BCCF-168B6A1AD4ED}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{0F728E4A-9D3A-423A-9118-0D98D7957E0C}">
       <text>
         <r>
           <rPr>
@@ -229,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{16839870-D1DB-4A6E-BA2C-55AFC3E94AD9}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{87D18172-C699-47E7-B90E-D0EF89FA6D8A}">
       <text>
         <r>
           <rPr>
@@ -329,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{486797B6-12D1-49A7-B527-7EBB7EF7AA5A}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{5F17F22D-B293-4F13-A5F9-FE686E62C809}">
       <text>
         <r>
           <rPr>
@@ -427,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{0B9A84C6-738B-4EF3-9979-E5D5B66C7407}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{B69D0E42-BF9E-4D81-860B-B3CA070A8B42}">
       <text>
         <r>
           <rPr>
@@ -517,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{DB778A24-0D49-4815-B82C-321D36FA156D}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C442BECD-4FE5-406F-8369-C90058B4C5E6}">
       <text>
         <r>
           <rPr>
@@ -665,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{85CFC2CF-C126-4AE9-A6BB-302CFE77F695}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{9B42E0B9-328A-43D9-8526-C229674B7285}">
       <text>
         <r>
           <rPr>
@@ -826,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{A6FD7804-2673-4FF8-8FBD-0EDFBE876C32}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{27DB8417-B15A-43E5-A616-0EA8DF59C2C9}">
       <text>
         <r>
           <rPr>
@@ -925,7 +933,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{F437A754-4A36-4634-900F-0295F0E00657}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{15959C1F-BA61-45DA-8ACF-47458B6D04DB}">
       <text>
         <r>
           <rPr>
@@ -951,7 +959,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{8B8AF1FA-578E-4F5C-A13B-2DD7E7C64726}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{FE2A7226-4FC7-4252-9927-C0B5D6C40367}">
       <text>
         <r>
           <rPr>
@@ -1124,7 +1132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{24ED9133-E675-4BBE-B8CD-60CDB818B4A6}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{9AC47F28-E98F-4D46-B044-DD386B4DCE2B}">
       <text>
         <r>
           <rPr>
@@ -1224,7 +1232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{F50FB37D-9D6F-4FBE-BD55-418D2080FE29}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{A63279E2-964D-40AE-BAD1-7B530BAE0C13}">
       <text>
         <r>
           <rPr>
@@ -1322,7 +1330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{D466BD6F-E46C-4FA0-8E4E-F59FE19E11F4}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{AF2E903D-E13D-4901-8704-03A069AB8E6E}">
       <text>
         <r>
           <rPr>
@@ -1412,7 +1420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{9BE6C63C-9B69-40C2-B038-F1587CF6E633}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{611FE63E-5B95-49D6-8FC2-C18099CA62CF}">
       <text>
         <r>
           <rPr>
@@ -1560,7 +1568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{A845B4D4-C2EC-49BA-871B-86B931FFA9C4}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{8F61E9E3-CB32-4689-B857-199148C0D5E9}">
       <text>
         <r>
           <rPr>
@@ -1721,7 +1729,3587 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{C6BFE0B2-313B-46C8-8AEB-B23D4DFF8997}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{5F7F5104-93FD-493F-9762-6F45C6B56C72}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>주행</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필수</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력사항입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.
+(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>소숫점입력불가</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>허승희</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{083643E4-2ABB-4F8A-930D-BB5C09201042}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사업자번호:  - 없이 입력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{A50853DE-6B6D-4703-A073-5D3F0DD47994}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업무용승용차등록</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>메뉴의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종에</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>자동</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>됩니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{23AA972E-15AD-4BCB-933E-4122ABA295EF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">업무용승용차등록의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">                </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호와</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{D35AE6AB-7598-493F-B4F4-42CEA1341C7B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기초</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규차량</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업로드시</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{972D19FF-45BF-4445-A09C-57B09C0BDB49}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>회계기간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도와</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8484DC55-1FF6-4AF0-AF8A-3D37FB248377}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>성명</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부서사원등록의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사원을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>먼저</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>등록하세요</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{94F462E2-D991-406A-94DD-74505EDD0009}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>항목</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{73159186-5697-40E1-8899-1965BAFEAFC7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>주행</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필수</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력사항입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.
+(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>소숫점입력불가</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>허승희</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{87167485-7593-42D9-9D69-35FD70B5EBA9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사업자번호:  - 없이 입력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{21AF5649-77F1-40DF-A6A3-41E17D451617}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업무용승용차등록</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>메뉴의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종에</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>자동</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>됩니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{8A107350-9601-49F1-B1BA-D0FDCD208595}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">업무용승용차등록의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">                </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호와</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{CD98427C-6FFA-4D23-A5E3-A39B7C0ABF2A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기초</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규차량</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업로드시</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{BE0E6052-6701-4CD3-8948-039A8328A244}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>회계기간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도와</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{76A93796-63B4-4314-83D0-1B364E29473C}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>성명</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부서사원등록의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사원을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>먼저</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>등록하세요</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{3E915F44-B587-4B50-8CFE-92D5BE3A1996}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>항목</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{683DA72A-E9E4-45D5-A71B-35B831D5186D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>주행</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필수</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력사항입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.
+(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>소숫점입력불가</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>허승희</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{CAAD54CA-B824-4D28-A5F8-21517D061837}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사업자번호:  - 없이 입력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{5729F43C-031C-4571-8F72-972D9EE37041}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업무용승용차등록</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>메뉴의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종에</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>자동</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>됩니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{05B3CA3F-6CDE-43DC-8E2C-EDA3440669D9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">업무용승용차등록의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">                </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호와</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{2585D7F2-6C4E-4320-B208-25F4533F9C4B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기초</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규차량</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업로드시</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{19B38334-A035-4B79-98BB-3F3B78988AE8}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>회계기간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도와</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{393FB187-867E-447F-8DBD-BEC3B31B09D1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>성명</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부서사원등록의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사원을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>먼저</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>등록하세요</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{E2011418-79AE-4FCE-B58E-F35996E76FFE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>항목</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{1928288D-80A1-48C0-B537-154A9D3D091C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>주행</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>필수</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력사항입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.
+(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>소숫점입력불가</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>허승희</author>
+  </authors>
+  <commentList>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{15A1A39C-F915-48AB-8ABE-245865B65A35}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사업자번호:  - 없이 입력</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="53"/>
+            <rFont val="맑은 고딕"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{0F8F4355-0945-46F1-B039-23F5A469DBC5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업무용승용차등록</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>메뉴의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차종에</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>자동</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>됩니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{C2D3564E-7C4F-4B92-A5F1-CFA67BCF3DC9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">업무용승용차등록의
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">                </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량번호와</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{82F54A90-ACA3-4481-A662-8C44757E7BB8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>기초</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">km : </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>신규차량</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>업로드시</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{49B18FA0-0516-4770-9C4B-7428E3F7F2A3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> : </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>회계기간</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>년도와</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>동일하게</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>작성</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B67EE0D2-CFD7-4172-B8B7-39E145DE6657}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>성명</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>부서사원등록의</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사원을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>먼저</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>등록하세요</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용자</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{2EE5AC4A-718C-4680-9723-681A95C49D6D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>차량의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>구분</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입력</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>항목</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>.</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{ABED181D-901B-4048-927D-5346AF3190E1}">
       <text>
         <r>
           <rPr>
@@ -1815,7 +5403,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="22">
   <si>
     <t>부서</t>
   </si>
@@ -2489,7 +6077,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F2019F9-C08F-AC2C-87F1-89D98612EB8C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AFBBE59-1982-9BD1-9D1F-9BAA4528393D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2954,7 +6542,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D48073E6-E26F-88CE-37BB-179A4039A156}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DD2A11D-74F2-3AF4-2F9E-A65FE2EAA2AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3234,7 +6822,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EFF0427-BDFD-42DA-AC19-7E42647C195B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B4CC06B-FD15-43B3-80FD-5C63ACB93773}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3699,7 +7287,2987 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9FFC9221-51EF-4824-B921-9E4CD0795E92}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAEC54C6-F777-4EC7-AAE6-E6C8A903CECD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8029575" y="2066925"/>
+          <a:ext cx="2095501" cy="1323975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비고 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>해당 숫자</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직접 내용 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>거래처방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>제조시설등 사업장방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회의참석</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>판촉활동</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>교육등 기타업무활동</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{929CA91A-4ADE-4C99-9433-7C1F58F17C83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8077200" y="219075"/>
+          <a:ext cx="3581400" cy="1438275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>※ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>명의구분 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>차량유형별 소유주 구분</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="800"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ 0.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>~ 2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>리스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>법</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>개</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>인 조정의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차관련비용명세서</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>에 반영되는 회사 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원소유의 차량 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>타인</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원외 타인 소유의 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)~7.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>렌트</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차가 아닌 회사가 관리하는 모든 차량</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A912FEBF-997D-46BF-A43F-256C79BE4E5C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8029575" y="2066925"/>
+          <a:ext cx="2095501" cy="1323975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비고 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>해당 숫자</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직접 내용 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>거래처방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>제조시설등 사업장방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회의참석</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>판촉활동</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>교육등 기타업무활동</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C45098E0-14CE-40FD-ACAB-2FC06D8858BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8077200" y="219075"/>
+          <a:ext cx="3581400" cy="1438275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>※ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>명의구분 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>차량유형별 소유주 구분</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="800"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ 0.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>~ 2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>리스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>법</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>개</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>인 조정의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차관련비용명세서</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>에 반영되는 회사 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원소유의 차량 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>타인</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원외 타인 소유의 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)~7.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>렌트</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차가 아닌 회사가 관리하는 모든 차량</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC076E88-4BE0-4A6F-93D6-B08C579D98BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8029575" y="2066925"/>
+          <a:ext cx="2095501" cy="1323975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비고 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>해당 숫자</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직접 내용 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>거래처방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>제조시설등 사업장방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회의참석</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>판촉활동</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>교육등 기타업무활동</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB932C3C-15FD-4DF2-AAE6-6D54D446314D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8077200" y="219075"/>
+          <a:ext cx="3581400" cy="1438275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>※ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>명의구분 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>차량유형별 소유주 구분</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="800"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ 0.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>~ 2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>리스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>법</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>개</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>인 조정의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차관련비용명세서</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>에 반영되는 회사 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원소유의 차량 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>타인</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원외 타인 소유의 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)~7.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>렌트</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차가 아닌 회사가 관리하는 모든 차량</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E5E2BF4-E479-4871-A578-F5A88287395C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8029575" y="2066925"/>
+          <a:ext cx="2095501" cy="1323975"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비고 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>해당 숫자</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직접 내용 입력</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>거래처방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>제조시설등 사업장방문</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회의참석</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>판촉활동</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="800">
+            <a:solidFill>
+              <a:srgbClr val="7030A0"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>교육등 기타업무활동</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940C7E17-BBF9-4BC0-BCE0-DB469D642C4D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8077200" y="219075"/>
+          <a:ext cx="3581400" cy="1438275"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>※ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>명의구분 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>차량유형별 소유주 구분</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="800"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ 0.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>~ 2.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>리스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)   </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>   : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>법</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>개</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>인 조정의 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>[</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차관련비용명세서</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>]</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>에 반영되는 회사 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원소유의 차량 </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1200"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>타인</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>직원외 타인 소유의 차량</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr>
+            <a:lnSpc>
+              <a:spcPts val="1100"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>○ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>회사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)~7.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>렌트</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>비</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) : </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="800" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>업무용승용차가 아닌 회사가 관리하는 모든 차량</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>114301</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D43AC0D-3F05-44DD-A593-1748A4498EF5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4216,7 +10784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF01455-E267-43CE-9B09-79A2EC381E9E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0725FC66-639F-4C9B-BF2A-DC9BB1F0512C}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4748,10 +11316,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{C6A085E8-371D-4B7E-8D00-B1EA21CB0E44}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{DE8BE9BD-9F90-4641-81BC-0404529A10E0}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{AD021761-02CD-4068-BDCC-99CB438F1249}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{68962381-DC27-4E4F-82A8-C6823B5264A1}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4765,7 +11333,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DECC3E6B-479A-468D-8AB6-BE36FAAC032D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90827B20-CA22-46AC-8967-BE4EA2C64BE0}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5297,10 +11865,2206 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{633F6023-D18D-4196-A452-84EAC496AF62}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{0A1D84D3-C096-4EB0-99FC-59F278091D18}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{0635E5A5-16FA-4F1C-8197-E92AC2ACB734}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{1C41738E-8026-4297-9AA4-F7E39F2F7F0D}">
+      <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D2C1AB-0CF5-48AA-9322-4226F8B1710A}">
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="4.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="39">
+        <v>1188121173</v>
+      </c>
+      <c r="E3" s="40"/>
+      <c r="F3" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="27"/>
+    </row>
+    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="47"/>
+      <c r="G7" s="19" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="15"/>
+    </row>
+    <row r="19" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="15"/>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="15"/>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="15"/>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="15"/>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="15"/>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="15"/>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="15"/>
+    </row>
+    <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G42" s="22" t="e">
+        <f>SUM(G11:G41,G7)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G43" s="22"/>
+      <c r="I43" s="22"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G45" s="22"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{8CD1668C-C627-4ADE-BA43-60C2AE112B4F}">
+      <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{6BC91F3B-501F-4503-87E2-09FF7FF28799}">
+      <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{035B9679-1C46-4899-B153-5A0575666863}">
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="4.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="39">
+        <v>1188121173</v>
+      </c>
+      <c r="E3" s="40"/>
+      <c r="F3" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="27"/>
+    </row>
+    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="47"/>
+      <c r="G7" s="19" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="15"/>
+    </row>
+    <row r="19" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="15"/>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="15"/>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="15"/>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="15"/>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="15"/>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="15"/>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="15"/>
+    </row>
+    <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G42" s="22" t="e">
+        <f>SUM(G11:G41,G7)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G43" s="22"/>
+      <c r="I43" s="22"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G45" s="22"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{FB59237A-851C-4CD9-8A35-0D88384AD521}">
+      <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{1C0F0E1C-5FA8-4B52-9CA5-2C07FD2E4FEE}">
+      <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CE8B26-7E9F-4747-87A4-92151E45C83A}">
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="4.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="39">
+        <v>1188121173</v>
+      </c>
+      <c r="E3" s="40"/>
+      <c r="F3" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="27"/>
+    </row>
+    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="47"/>
+      <c r="G7" s="19" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="15"/>
+    </row>
+    <row r="19" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="15"/>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="15"/>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="15"/>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="15"/>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="15"/>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="15"/>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="15"/>
+    </row>
+    <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G42" s="22" t="e">
+        <f>SUM(G11:G41,G7)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G43" s="22"/>
+      <c r="I43" s="22"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G45" s="22"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{3194DEB3-5025-44EE-AFD1-FBF1B7ED2C60}">
+      <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{A2D511DA-58B9-46E2-BE84-4D3EA48EFC38}">
+      <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="95" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64A210E-6ADA-45C0-A340-89C171475BAA}">
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="4.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="39">
+        <v>1188121173</v>
+      </c>
+      <c r="E3" s="40"/>
+      <c r="F3" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="27"/>
+    </row>
+    <row r="4" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="46"/>
+      <c r="G6" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="47"/>
+      <c r="G7" s="19" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="26"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" s="4" customFormat="1" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="29"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="15"/>
+    </row>
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="15"/>
+    </row>
+    <row r="17" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="15"/>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="15"/>
+    </row>
+    <row r="19" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="15"/>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="15"/>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="15"/>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="15"/>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="15"/>
+    </row>
+    <row r="27" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="15"/>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="15"/>
+    </row>
+    <row r="29" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="15"/>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="15"/>
+    </row>
+    <row r="32" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="15"/>
+    </row>
+    <row r="33" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="15"/>
+    </row>
+    <row r="34" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="15"/>
+    </row>
+    <row r="35" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="15"/>
+    </row>
+    <row r="36" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="15"/>
+    </row>
+    <row r="37" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="15"/>
+    </row>
+    <row r="38" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="15"/>
+    </row>
+    <row r="39" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="15"/>
+    </row>
+    <row r="40" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="15"/>
+    </row>
+    <row r="41" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="15"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G42" s="22" t="e">
+        <f>SUM(G11:G41,G7)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G43" s="22"/>
+      <c r="I43" s="22"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G45" s="22"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <mergeCells count="10">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{84926DC9-B7B2-493A-9776-DB7DD7E01E62}">
+      <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{8FBBD658-71A0-4BF9-9536-21CA3BD5D3BA}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
   </dataValidations>

--- a/backend/app/modules/safety_ledgers/templates/company-vehicle-template.xlsx
+++ b/backend/app/modules/safety_ledgers/templates/company-vehicle-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JSI\besma-safety-ledgers-deploy\backend\app\modules\safety_ledgers\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{88B07AF5-0C9F-4C4C-9793-9509B9B9D903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7C9E6A9C-AC07-4AA3-810F-17DD9E5313F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{CB2AFB4F-771C-472A-8EBD-756E310E9CF4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{B6893C91-BA84-4112-BBBC-7FC3BE855389}"/>
   </bookViews>
   <sheets>
     <sheet name="7월" sheetId="16" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{E2C23149-5D37-4375-85CB-6F3C70B004DE}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{93342067-875A-455D-BA81-3E6BB958AF84}">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{0F728E4A-9D3A-423A-9118-0D98D7957E0C}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{934BACA3-2D2B-4868-8BE8-27237CC6CAAD}">
       <text>
         <r>
           <rPr>
@@ -237,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{87D18172-C699-47E7-B90E-D0EF89FA6D8A}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{3ACE5118-F284-4CF1-AFB7-60D3F7B4AB9B}">
       <text>
         <r>
           <rPr>
@@ -337,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{5F17F22D-B293-4F13-A5F9-FE686E62C809}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{13270A86-92BB-4488-B50B-611A9D23B261}">
       <text>
         <r>
           <rPr>
@@ -435,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{B69D0E42-BF9E-4D81-860B-B3CA070A8B42}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{8A1A5ED1-8154-4447-A893-586DBB3D6BE0}">
       <text>
         <r>
           <rPr>
@@ -525,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{C442BECD-4FE5-406F-8369-C90058B4C5E6}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{07A9CB57-370F-4825-866D-24DB04320BB0}">
       <text>
         <r>
           <rPr>
@@ -673,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{9B42E0B9-328A-43D9-8526-C229674B7285}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{538B5BB7-8071-4B9A-A91E-80F5788460B6}">
       <text>
         <r>
           <rPr>
@@ -834,7 +834,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{27DB8417-B15A-43E5-A616-0EA8DF59C2C9}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{2CB2F630-739C-4EB2-9C23-73739A99A0AA}">
       <text>
         <r>
           <rPr>
@@ -933,7 +933,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{15959C1F-BA61-45DA-8ACF-47458B6D04DB}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{E82A7EF8-31A1-40FF-9F68-9768A7EAF824}">
       <text>
         <r>
           <rPr>
@@ -959,7 +959,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{FE2A7226-4FC7-4252-9927-C0B5D6C40367}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{63D97036-D15A-4816-8F10-7BBFB51AE28B}">
       <text>
         <r>
           <rPr>
@@ -1132,7 +1132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{9AC47F28-E98F-4D46-B044-DD386B4DCE2B}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{AED5AF79-E62B-42C3-B529-E3A43CF267B1}">
       <text>
         <r>
           <rPr>
@@ -1232,7 +1232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{A63279E2-964D-40AE-BAD1-7B530BAE0C13}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{5D72941C-84DC-4594-B355-425DA9E6D2CE}">
       <text>
         <r>
           <rPr>
@@ -1330,7 +1330,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{AF2E903D-E13D-4901-8704-03A069AB8E6E}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{8908EA15-8AF6-427C-BAB0-F8C99B8D990B}">
       <text>
         <r>
           <rPr>
@@ -1420,7 +1420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{611FE63E-5B95-49D6-8FC2-C18099CA62CF}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B7E8C2D7-54A8-464C-B612-3B2296592291}">
       <text>
         <r>
           <rPr>
@@ -1568,7 +1568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{8F61E9E3-CB32-4689-B857-199148C0D5E9}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{3D68BEA6-F045-46B2-BA35-163934AF5FB9}">
       <text>
         <r>
           <rPr>
@@ -1729,7 +1729,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{5F7F5104-93FD-493F-9762-6F45C6B56C72}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{B952A7E4-33E5-4DCD-B4F2-B9774BDBC50E}">
       <text>
         <r>
           <rPr>
@@ -1828,7 +1828,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{083643E4-2ABB-4F8A-930D-BB5C09201042}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{84C09689-06D3-4C3C-BB58-C29D8EAE17FC}">
       <text>
         <r>
           <rPr>
@@ -1854,7 +1854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{A50853DE-6B6D-4703-A073-5D3F0DD47994}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{5EACA249-84B9-4EE4-B213-1661F82C8609}">
       <text>
         <r>
           <rPr>
@@ -2027,7 +2027,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{23AA972E-15AD-4BCB-933E-4122ABA295EF}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{1F4576E5-9DEC-44E7-8142-EEE04C310CAD}">
       <text>
         <r>
           <rPr>
@@ -2127,7 +2127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{D35AE6AB-7598-493F-B4F4-42CEA1341C7B}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{0EA6B57D-8F0A-416F-B9A4-4CF5B13B855C}">
       <text>
         <r>
           <rPr>
@@ -2225,7 +2225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{972D19FF-45BF-4445-A09C-57B09C0BDB49}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{5B6D0B39-9DFD-48AC-93D0-F70CAF0FC668}">
       <text>
         <r>
           <rPr>
@@ -2315,7 +2315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{8484DC55-1FF6-4AF0-AF8A-3D37FB248377}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{A7D2A9B5-6595-4A4B-B76B-DE833B034EDC}">
       <text>
         <r>
           <rPr>
@@ -2463,7 +2463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{94F462E2-D991-406A-94DD-74505EDD0009}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{7C585D71-186D-458D-BEE2-286BD1082489}">
       <text>
         <r>
           <rPr>
@@ -2624,7 +2624,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{73159186-5697-40E1-8899-1965BAFEAFC7}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{6564B96A-BCBA-4349-8646-679AFC221D7C}">
       <text>
         <r>
           <rPr>
@@ -2723,7 +2723,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{87167485-7593-42D9-9D69-35FD70B5EBA9}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{4FAFC940-A094-452D-A36E-933578F65A3E}">
       <text>
         <r>
           <rPr>
@@ -2749,7 +2749,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{21AF5649-77F1-40DF-A6A3-41E17D451617}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{D4C66204-7263-4D56-8437-CEBA4FC53DB9}">
       <text>
         <r>
           <rPr>
@@ -2922,7 +2922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{8A107350-9601-49F1-B1BA-D0FDCD208595}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{0DAF2001-56C6-4CBF-BA7F-8C98D001A678}">
       <text>
         <r>
           <rPr>
@@ -3022,7 +3022,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{CD98427C-6FFA-4D23-A5E3-A39B7C0ABF2A}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{F6599236-4740-4532-8CE2-57001BBDD186}">
       <text>
         <r>
           <rPr>
@@ -3120,7 +3120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{BE0E6052-6701-4CD3-8948-039A8328A244}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{335362C9-2A85-42A8-87C6-B6CA64113742}">
       <text>
         <r>
           <rPr>
@@ -3210,7 +3210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{76A93796-63B4-4314-83D0-1B364E29473C}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{800E342C-0C22-4BD5-9011-14FD23F6F1BF}">
       <text>
         <r>
           <rPr>
@@ -3358,7 +3358,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{3E915F44-B587-4B50-8CFE-92D5BE3A1996}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{DDCC7797-9027-44C7-B735-D0EF049B999A}">
       <text>
         <r>
           <rPr>
@@ -3519,7 +3519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{683DA72A-E9E4-45D5-A71B-35B831D5186D}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{873014A0-1913-4386-91BE-C2E9814142FB}">
       <text>
         <r>
           <rPr>
@@ -3618,7 +3618,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{CAAD54CA-B824-4D28-A5F8-21517D061837}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{BCE24386-8BCF-4A1A-8EB9-4C7E0CCE1057}">
       <text>
         <r>
           <rPr>
@@ -3644,7 +3644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{5729F43C-031C-4571-8F72-972D9EE37041}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{668477A1-04FB-40CE-9104-A79D8BBE271E}">
       <text>
         <r>
           <rPr>
@@ -3817,7 +3817,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{05B3CA3F-6CDE-43DC-8E2C-EDA3440669D9}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{27450D01-1638-45C3-993A-4CEBDB1A02F7}">
       <text>
         <r>
           <rPr>
@@ -3917,7 +3917,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{2585D7F2-6C4E-4320-B208-25F4533F9C4B}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{2F77793D-31FE-4FE1-A84C-CEC97DB86E30}">
       <text>
         <r>
           <rPr>
@@ -4015,7 +4015,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{19B38334-A035-4B79-98BB-3F3B78988AE8}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{9583C174-D42C-44CE-B890-ADA61F98F403}">
       <text>
         <r>
           <rPr>
@@ -4105,7 +4105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{393FB187-867E-447F-8DBD-BEC3B31B09D1}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{226BF609-71DC-4097-99DF-E620DB4040B2}">
       <text>
         <r>
           <rPr>
@@ -4253,7 +4253,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{E2011418-79AE-4FCE-B58E-F35996E76FFE}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{60E61C84-1033-406A-A7C1-808F94F9C95A}">
       <text>
         <r>
           <rPr>
@@ -4414,7 +4414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{1928288D-80A1-48C0-B537-154A9D3D091C}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{381DFF36-DDA1-4BFF-8857-2C22FAD538B3}">
       <text>
         <r>
           <rPr>
@@ -4513,7 +4513,7 @@
     <author>허승희</author>
   </authors>
   <commentList>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{15A1A39C-F915-48AB-8ABE-245865B65A35}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{0F201112-9460-418F-8346-B821C64D6416}">
       <text>
         <r>
           <rPr>
@@ -4539,7 +4539,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{0F8F4355-0945-46F1-B039-23F5A469DBC5}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{95D1538C-D8CF-4338-8B12-0B12F963004B}">
       <text>
         <r>
           <rPr>
@@ -4712,7 +4712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{C2D3564E-7C4F-4B92-A5F1-CFA67BCF3DC9}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{8A9BDFE7-BF34-4376-998A-314AABE0E3DC}">
       <text>
         <r>
           <rPr>
@@ -4812,7 +4812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{82F54A90-ACA3-4481-A662-8C44757E7BB8}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{93F5CAB4-2697-42E3-ADF3-3FDF8F1C033C}">
       <text>
         <r>
           <rPr>
@@ -4910,7 +4910,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{49B18FA0-0516-4770-9C4B-7428E3F7F2A3}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{AE6EACF6-4277-4663-828B-C2A2200337E8}">
       <text>
         <r>
           <rPr>
@@ -5000,7 +5000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{B67EE0D2-CFD7-4172-B8B7-39E145DE6657}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{DDA6C177-327A-4671-8668-6E2A306FB427}">
       <text>
         <r>
           <rPr>
@@ -5148,7 +5148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{2EE5AC4A-718C-4680-9723-681A95C49D6D}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{2B507606-FEC1-4E71-AE9D-0583E82B1CAC}">
       <text>
         <r>
           <rPr>
@@ -5309,7 +5309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{ABED181D-901B-4048-927D-5346AF3190E1}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{1D4705F9-24B9-43E5-8291-E7725F981D7E}">
       <text>
         <r>
           <rPr>
@@ -6077,7 +6077,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AFBBE59-1982-9BD1-9D1F-9BAA4528393D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB521832-A073-6FDC-48D4-AF6EB8AD940F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6542,7 +6542,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DD2A11D-74F2-3AF4-2F9E-A65FE2EAA2AF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{225F0241-C1CB-D1A3-EE22-87E8B9B91181}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6822,7 +6822,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B4CC06B-FD15-43B3-80FD-5C63ACB93773}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F8FD587-6333-4369-80A4-7FBBE3BD83F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7287,7 +7287,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAEC54C6-F777-4EC7-AAE6-E6C8A903CECD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CB2E03E-E237-4A89-9DA2-AA03629788CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7567,7 +7567,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{929CA91A-4ADE-4C99-9433-7C1F58F17C83}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88F54AEC-25B2-4C72-8C42-84BB97CD1D40}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8032,7 +8032,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A912FEBF-997D-46BF-A43F-256C79BE4E5C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEE3E9A7-ED0E-4416-BC81-CD6CFE8FF7CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8312,7 +8312,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C45098E0-14CE-40FD-ACAB-2FC06D8858BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09B0D424-DFCD-4FC2-99D8-581EC1AD3603}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -8777,7 +8777,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC076E88-4BE0-4A6F-93D6-B08C579D98BC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8767B58C-DCC4-4374-90B4-0433362F1EA3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9057,7 +9057,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB932C3C-15FD-4DF2-AAE6-6D54D446314D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DEB37F5-9A4A-4414-9603-DD9CBD6A0360}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9522,7 +9522,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E5E2BF4-E479-4871-A578-F5A88287395C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66266F40-636A-44BA-A9A3-3A397A7D68F8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9802,7 +9802,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{940C7E17-BBF9-4BC0-BCE0-DB469D642C4D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0940FE05-9BF7-407A-B8AD-8AF766B727D7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10267,7 +10267,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D43AC0D-3F05-44DD-A593-1748A4498EF5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A8B5DF2-3E0F-4BE4-B630-B73CDF908194}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10784,7 +10784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0725FC66-639F-4C9B-BF2A-DC9BB1F0512C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EDAAC60-15B9-4839-A8E0-B3E38546B798}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10909,10 +10909,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="47"/>
-      <c r="G7" s="19" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="23" t="s">
         <v>15</v>
       </c>
@@ -11288,9 +11285,9 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G42" s="22" t="e">
-        <f>SUM(G11:G41,G7)</f>
-        <v>#REF!</v>
+      <c r="G42" s="22">
+        <f>SUM(G11:G41)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -11316,10 +11313,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{DE8BE9BD-9F90-4641-81BC-0404529A10E0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{6BDE797B-FEBB-459D-BE21-3E79A8417490}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{68962381-DC27-4E4F-82A8-C6823B5264A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{CF5B812B-809C-4DBF-9B34-0C85196F2694}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11333,7 +11330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90827B20-CA22-46AC-8967-BE4EA2C64BE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C8218F-34C5-4CF9-9BE9-6EBC6A27525A}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11458,10 +11455,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="47"/>
-      <c r="G7" s="19" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="23" t="s">
         <v>15</v>
       </c>
@@ -11837,9 +11831,9 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G42" s="22" t="e">
-        <f>SUM(G11:G41,G7)</f>
-        <v>#REF!</v>
+      <c r="G42" s="22">
+        <f>SUM(G11:G41)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -11865,10 +11859,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{0A1D84D3-C096-4EB0-99FC-59F278091D18}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{5C08C813-5F0D-4975-A40B-0101DDB229C5}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{1C41738E-8026-4297-9AA4-F7E39F2F7F0D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{6ECC04F8-4009-4C63-965E-2D85BB8F8410}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11882,7 +11876,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03D2C1AB-0CF5-48AA-9322-4226F8B1710A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA7FA6BE-9A0A-4240-B5AA-FB430250D19A}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12007,10 +12001,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="47"/>
-      <c r="G7" s="19" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="23" t="s">
         <v>15</v>
       </c>
@@ -12386,9 +12377,9 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G42" s="22" t="e">
-        <f>SUM(G11:G41,G7)</f>
-        <v>#REF!</v>
+      <c r="G42" s="22">
+        <f>SUM(G11:G41)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -12414,10 +12405,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{8CD1668C-C627-4ADE-BA43-60C2AE112B4F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{67F26B9A-1C8D-4FDE-A4B7-40871C408B91}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{6BC91F3B-501F-4503-87E2-09FF7FF28799}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{613E3230-A62F-4330-B2BC-120294CF615A}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12431,7 +12422,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{035B9679-1C46-4899-B153-5A0575666863}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1CF8BD-799C-4582-8D14-9D77046A9DD0}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12556,10 +12547,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="47"/>
-      <c r="G7" s="19" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="23" t="s">
         <v>15</v>
       </c>
@@ -12935,9 +12923,9 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G42" s="22" t="e">
-        <f>SUM(G11:G41,G7)</f>
-        <v>#REF!</v>
+      <c r="G42" s="22">
+        <f>SUM(G11:G41)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -12963,10 +12951,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{FB59237A-851C-4CD9-8A35-0D88384AD521}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{3C3B9029-44DE-443E-83DE-2C955AC2FCF7}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{1C0F0E1C-5FA8-4B52-9CA5-2C07FD2E4FEE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{D4667D26-8E5D-44FA-9812-6C0BA0ED41E5}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12980,7 +12968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CE8B26-7E9F-4747-87A4-92151E45C83A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF944FE-F352-4127-AAFD-10FD77121B06}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13105,10 +13093,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="47"/>
-      <c r="G7" s="19" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="23" t="s">
         <v>15</v>
       </c>
@@ -13484,9 +13469,9 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G42" s="22" t="e">
-        <f>SUM(G11:G41,G7)</f>
-        <v>#REF!</v>
+      <c r="G42" s="22">
+        <f>SUM(G11:G41)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -13512,10 +13497,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{3194DEB3-5025-44EE-AFD1-FBF1B7ED2C60}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{F8EF5814-C6AC-4420-B824-22D033FB72BB}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{A2D511DA-58B9-46E2-BE84-4D3EA48EFC38}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{107BC723-3E3B-4B0C-8CE9-9E061774B5F6}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13529,7 +13514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64A210E-6ADA-45C0-A340-89C171475BAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42BA3921-35A5-4E38-A39E-C8D5429DB6A2}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13654,10 +13639,7 @@
         <v>21</v>
       </c>
       <c r="F7" s="47"/>
-      <c r="G7" s="19" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G7" s="19"/>
       <c r="H7" s="23" t="s">
         <v>15</v>
       </c>
@@ -14033,9 +14015,9 @@
       <c r="H41" s="15"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G42" s="22" t="e">
-        <f>SUM(G11:G41,G7)</f>
-        <v>#REF!</v>
+      <c r="G42" s="22">
+        <f>SUM(G11:G41)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -14061,10 +14043,10 @@
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{84926DC9-B7B2-493A-9776-DB7DD7E01E62}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7" xr:uid="{EAB022D4-FBDC-4429-B418-8B409D0806CD}">
       <formula1>"0.회사,1.렌트,2.리스,3.직원,4.타인,5.회사(비),6.리스(비),7.렌트(비)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{8FBBD658-71A0-4BF9-9536-21CA3BD5D3BA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10:F41" xr:uid="{6B7E3B7F-84B4-42CE-9A4F-9C6302EDA77E}">
       <formula1>"1.출근용,2.퇴근용,3.업무용,4.비업무용(개인),5.출퇴근용(왕복),6.업무용(왕복),7.비업무용(왕복)"</formula1>
     </dataValidation>
   </dataValidations>
